--- a/controle_banco_horas.xlsx
+++ b/controle_banco_horas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Data ISO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Marcações</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Horas Trabalhadas</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Abonas</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Carga Horária</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Banco do Dia</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Saldo Acumulado</t>
         </is>
@@ -473,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -511,22 +499,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>06:56 | 13:36 | 14:57 | 16:29</t>
-        </is>
-      </c>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -541,34 +525,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>06:59 | 13:42 | 14:42 | 16:17</t>
-        </is>
-      </c>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -583,34 +563,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00:51</t>
+          <t>00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:55 | 13:27 | 14:32 | 16:00</t>
+          <t>07:10 | 13:15 | 14:15 | 16:27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -625,34 +605,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00:51</t>
+          <t>00:17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06:58 | 13:30 | 14:32 | 16:17</t>
+          <t>07:14 | 12:54 | 13:54 | 17:15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -667,34 +647,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>01:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>07:00 | 12:11 | 13:05 | 16:08</t>
+          <t>07:21 | 12:55 | 13:55 | 16:08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -709,34 +689,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>-00:13</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01:24</t>
+          <t>01:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07:00 | 13:27 | 14:27 | 16:06</t>
+          <t>06:59 | 13:46 | 14:47 | 16:28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -751,34 +731,34 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>00:06</t>
+          <t>00:28</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07:04 | 13:28 | 14:28 | 16:15</t>
+          <t>06:58 | 13:44 | 14:45 | 16:07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -793,7 +773,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -805,22 +785,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06:59 | 13:21 | 14:35 | 16:12</t>
+          <t>07:00 | 12:15 | 13:11 | 16:18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -835,34 +815,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>00:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01:54</t>
+          <t>02:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>07:02 | 12:17 | 13:23 | 16:08</t>
+          <t>07:01 | 13:47 | 14:47 | 16:29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -877,34 +857,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01:54</t>
+          <t>02:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>07:00 | 14:12 | 15:24 | 16:21</t>
+          <t>07:16 | 13:54 | 14:55 | 17:09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -919,34 +899,34 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>00:52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>02:27</t>
+          <t>03:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>07:02 | 13:20 | 14:20 | 15:20</t>
+          <t>07:07 | 13:33 | 14:32 | 16:20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -961,30 +941,34 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>00:42</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>03:09</t>
+          <t>03:37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>07:21 | 12:17 | 13:24 | 16:35</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -999,34 +983,34 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:07</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>03:09</t>
+          <t>03:44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06:59 | 13:35 | 14:35 | 16:19</t>
+          <t>07:06 | 13:45 | 14:45 | 16:41</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1041,34 +1025,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>00:20</t>
+          <t>00:35</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>03:29</t>
+          <t>04:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06:59 | 12:02 | 13:05 | 16:26</t>
+          <t>07:10 | 12:30 | 13:32 | 17:26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1083,34 +1067,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>01:14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>05:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>07:03 | 12:30 | 13:30 | 16:07</t>
+          <t>07:08 | 13:40 | 14:40 | 16:31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1125,34 +1109,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>00:04</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>07:05 | 13:24 | 14:36 | 16:07</t>
+          <t>07:07 | 13:42 | 14:42 | 16:21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1167,34 +1151,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-00:10</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>06:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>07:01 | 13:22 | 14:24 | 16:42</t>
+          <t>07:01 | 13:37 | 14:35 | 16:13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1209,34 +1193,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>04:31</t>
+          <t>06:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06:59 | 13:15 | 14:14 | 16:17</t>
+          <t>07:16 | 13:37 | 14:37 | 16:21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1251,34 +1235,34 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>04:49</t>
+          <t>06:29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07:03 | 12:26 | 13:26 | 16:21</t>
+          <t>07:10 | 13:24 | 14:24 | 16:41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1293,34 +1277,34 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>05:07</t>
+          <t>07:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>14/03/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07:11 | 12:16 | 13:34 | 16:15</t>
+          <t>07:09 | 12:35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>05:26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1335,34 +1319,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>-02:34</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>05:25</t>
+          <t>04:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07:09 | 13:25 | 14:25 | 16:14</t>
+          <t>07:05 | 13:55 | 14:53 | 16:16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1377,34 +1361,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>07:19 | 13:37 | 14:37 | 16:15</t>
+          <t>07:12 | 13:32 | 14:31 | 16:25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1419,34 +1403,34 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-00:04</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>05:26</t>
+          <t>04:53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>07:03 | 13:17 | 14:25 | 16:27</t>
+          <t>07:08 | 12:21 | 13:20 | 16:27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1461,34 +1445,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>00:20</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>07:09 | 12:15 | 13:17 | 16:16</t>
+          <t>07:00 | 13:27 | 14:26 | 16:36</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1503,34 +1487,34 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>00:37</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>07:13 | 13:52 | 15:00 | 16:23</t>
+          <t>07:03 | 13:00 | 14:01 | 16:44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1545,30 +1529,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>06:30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>07:04 | 13:27 | 14:27 | 16:22</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1583,30 +1571,34 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:18</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>06:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>07:05 | 13:41 | 14:41 | 16:45</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1621,34 +1613,34 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>07:28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>06:57 | 13:40 | 14:40 | 16:20</t>
+          <t>07:03 | 13:30 | 14:30 | 16:14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1663,34 +1655,34 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>00:23</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>07:00 | 12:31 | 13:31 | 16:00</t>
+          <t>07:15 | 13:25 | 14:27 | 16:27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1705,34 +1697,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07:00 | 11:53 | 12:59 | 16:11</t>
+          <t>07:22 | 13:25 | 14:25 | 16:23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1747,34 +1739,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07:03 | 12:07 | 13:08 | 16:35</t>
+          <t>07:12 | 12:22 | 13:28 | 16:27</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1789,34 +1781,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>00:32</t>
+          <t>00:09</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>07:59</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07:03 | 13:48 | 14:57 | 16:08</t>
+          <t>06:56 | 12:15 | 13:14 | 16:25</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1831,34 +1823,34 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-00:04</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>08:29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07:09 | 12:00 | 13:02 | 16:08</t>
+          <t>07:06 | 12:10 | 13:10 | 16:37</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1873,34 +1865,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-00:03</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>07:12 | 13:13 | 14:13 | 16:12</t>
-        </is>
-      </c>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1920,29 +1908,25 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>07:10 | 14:36 | 15:36 | 16:35</t>
-        </is>
-      </c>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1957,34 +1941,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>00:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07:22 | 12:09 | 13:07 | 16:06</t>
+          <t>07:02 | 12:18 | 13:18 | 16:10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1999,34 +1983,34 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-00:16</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07:09 | 12:39 | 13:31 | 16:29</t>
+          <t>07:26 | 12:16 | 13:12 | 16:28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2041,30 +2025,34 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>00:28</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>06:58 | 13:43 | 14:42 | 16:07</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2079,34 +2067,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>09:24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07:00 | 12:00 | 13:00 | 16:20</t>
+          <t>07:08 | 13:09 | 14:09 | 16:06</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2121,34 +2109,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>00:20</t>
+          <t>-00:02</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>09:22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07:00 | 12:19 | 13:19 | 16:33</t>
+          <t>06:58 | 13:32 | 14:32 | 16:03</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2163,34 +2151,34 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>06:59 | 12:08 | 13:10 | 16:40</t>
+          <t>07:08 | 13:56 | 16:07</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2205,34 +2193,34 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>07:05 | 12:00 | 13:00 | 16:40</t>
+          <t>07:05 | 13:32 | 14:32 | 16:11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2247,938 +2235,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>15/12/2025</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>07:01 | 12:22 | 14:19 | 16:21</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>07:23</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>00:20</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>06:58 | 13:14 | 14:16 | 16:13</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>08:13</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>17/12/2025</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>07:14 | 12:47 | 13:48 | 16:14</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-00:01</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>18/12/2025</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>07:01 | 12:00 | 13:00 | 16:13</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>08:12</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>00:12</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>19/12/2025</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>07:00 | 11:00</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-04:00</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>22/12/2025</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>23/12/2025</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>24/12/2025</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>25/12/2025</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>26/12/2025</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>29/12/2025</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>30/12/2025</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>31/12/2025</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>02/01/2026</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>06:56 | 12:00 | 13:00 | 16:00</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>00:04</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>06:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>07:06 | 13:23 | 14:23 | 16:13</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>08:07</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>00:07</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>06:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>07:00 | 13:05 | 14:05 | 16:21</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>00:21</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>07:00 | 12:24 | 13:24 | 16:00</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>07:00 | 12:16 | 13:13 | 16:02</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>00:05</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>12/01/2026</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>07:02 | 12:38 | 13:38 | 17:30</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>01:28</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>13/01/2026</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>07:21 | 12:00 | 13:00 | 16:21</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>14/01/2026</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>08:00 | 11:34 | 12:34 | 16:05</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-00:55</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>07:33</t>
+          <t>09:33</t>
         </is>
       </c>
     </row>
